--- a/VerveStacks_NOR_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NOR_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CEBA94F-E204-4B5E-A3F5-61148194C400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BF1C94D-EF76-4B4A-8347-69D3A8B10FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -762,48 +762,54 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_NOR_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_NOR_003</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_NOR_009</t>
   </si>
   <si>
@@ -822,37 +828,79 @@
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_solelc_spv_NOR_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_r8890887_NOR,e_r11981383_NOR</t>
+  </si>
+  <si>
+    <t>e_r7928148_NOR,e_NO90-420_NOR</t>
+  </si>
+  <si>
+    <t>e_w60495669-420_NOR</t>
+  </si>
+  <si>
+    <t>e_r11981383_NOR,e_r7928148_NOR</t>
+  </si>
+  <si>
+    <t>e_NO90-420_NOR,e_w60495669-420_NOR</t>
+  </si>
+  <si>
     <t>e_r12832053_NOR,e_r8890887_NOR</t>
   </si>
   <si>
-    <t>e_w60495669-420_NOR</t>
-  </si>
-  <si>
-    <t>e_r11981383_NOR,e_r7928148_NOR</t>
-  </si>
-  <si>
-    <t>e_r8890887_NOR,e_r11981383_NOR</t>
-  </si>
-  <si>
-    <t>e_r7928148_NOR,e_NO90-420_NOR</t>
-  </si>
-  <si>
     <t>e_r12832053_NOR</t>
   </si>
   <si>
-    <t>e_NO90-420_NOR,e_w60495669-420_NOR</t>
+    <t>distr_wonelc_won_NOR_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wonelc_won_NOR_006</t>
@@ -867,52 +915,43 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_NOR_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>elc_won_NOR_005</t>
+  </si>
+  <si>
+    <t>e_r12832053_NOR,e_r7928148_NOR,e_NO90-420_NOR</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_001</t>
+  </si>
+  <si>
+    <t>e_NO90-420_NOR</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_002</t>
+  </si>
+  <si>
+    <t>e_r8890887_NOR</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_010</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_009</t>
+  </si>
+  <si>
+    <t>e_r7928148_NOR,e_NO90-420_NOR,e_w60495669-420_NOR</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_008</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_007</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_004</t>
+  </si>
+  <si>
+    <t>e_r7928148_NOR,e_r12832053_NOR,e_NO90-420_NOR</t>
   </si>
   <si>
     <t>elc_won_NOR_006</t>
@@ -921,415 +960,376 @@
     <t>elc_won_NOR_003</t>
   </si>
   <si>
-    <t>elc_won_NOR_005</t>
-  </si>
-  <si>
-    <t>e_r12832053_NOR,e_r7928148_NOR,e_NO90-420_NOR</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_001</t>
-  </si>
-  <si>
-    <t>e_NO90-420_NOR</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_008</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_002</t>
-  </si>
-  <si>
-    <t>e_r8890887_NOR</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_010</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_009</t>
-  </si>
-  <si>
-    <t>e_r7928148_NOR,e_NO90-420_NOR,e_w60495669-420_NOR</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_004</t>
-  </si>
-  <si>
-    <t>e_r7928148_NOR,e_r12832053_NOR,e_NO90-420_NOR</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_007</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_NOR_011</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_NOR_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_NOR_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_NOR_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
     <t>elc_wof_NOR_011</t>
   </si>
   <si>
     <t>e_NO5-400_NOR,e_FI1-220_NOR</t>
   </si>
   <si>
+    <t>elc_wof_NOR_024</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_035</t>
+  </si>
+  <si>
+    <t>e_NO55-300_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_012</t>
+  </si>
+  <si>
+    <t>e_NO5-400_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_008</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_030</t>
+  </si>
+  <si>
+    <t>e_NO27-420_NOR,e_w254428135-420_NOR,e_r8473044-220_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_006</t>
+  </si>
+  <si>
+    <t>e_FI1-220_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_025</t>
+  </si>
+  <si>
+    <t>e_NO15-420_NOR,e_NO5-400_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_001</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_028</t>
+  </si>
+  <si>
+    <t>e_r8473044-220_NOR,e_NO15-420_NOR,e_NO5-400_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_002</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_005</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_007</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_034</t>
+  </si>
+  <si>
+    <t>e_NO55-300_NOR,e_NO27-420_NOR,e_w254428135-420_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_036</t>
+  </si>
+  <si>
+    <t>e_NO55-300_NOR,e_NO27-420_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_019</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_017</t>
+  </si>
+  <si>
+    <t>e_r12832053_NOR,e_NO55-300_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_023</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_015</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_016</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_022</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_021</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_010</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_009</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_033</t>
+  </si>
+  <si>
+    <t>e_NO27-420_NOR,e_w254428135-420_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_029</t>
+  </si>
+  <si>
+    <t>e_r8473044-220_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_026</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_013</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_020</t>
+  </si>
+  <si>
+    <t>e_r11981383_NOR,e_r8890887_NOR,e_r7928148_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_018</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_032</t>
+  </si>
+  <si>
+    <t>e_w254428135-420_NOR,e_r8473044-220_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_014</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_031</t>
+  </si>
+  <si>
+    <t>e_w254428135-420_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_027</t>
+  </si>
+  <si>
+    <t>e_r8473044-220_NOR,e_NO15-420_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_004</t>
+  </si>
+  <si>
     <t>elc_wof_NOR_003</t>
-  </si>
-  <si>
-    <t>e_FI1-220_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_025</t>
-  </si>
-  <si>
-    <t>e_NO15-420_NOR,e_NO5-400_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_001</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_017</t>
-  </si>
-  <si>
-    <t>e_r12832053_NOR,e_NO55-300_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_023</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_015</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_007</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_034</t>
-  </si>
-  <si>
-    <t>e_NO55-300_NOR,e_NO27-420_NOR,e_w254428135-420_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_036</t>
-  </si>
-  <si>
-    <t>e_NO55-300_NOR,e_NO27-420_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_019</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_031</t>
-  </si>
-  <si>
-    <t>e_w254428135-420_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_027</t>
-  </si>
-  <si>
-    <t>e_r8473044-220_NOR,e_NO15-420_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_004</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_020</t>
-  </si>
-  <si>
-    <t>e_r11981383_NOR,e_r8890887_NOR,e_r7928148_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_018</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_032</t>
-  </si>
-  <si>
-    <t>e_w254428135-420_NOR,e_r8473044-220_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_014</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_030</t>
-  </si>
-  <si>
-    <t>e_NO27-420_NOR,e_w254428135-420_NOR,e_r8473044-220_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_006</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_016</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_022</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_021</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_010</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_009</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_028</t>
-  </si>
-  <si>
-    <t>e_r8473044-220_NOR,e_NO15-420_NOR,e_NO5-400_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_002</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_005</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_024</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_035</t>
-  </si>
-  <si>
-    <t>e_NO55-300_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_012</t>
-  </si>
-  <si>
-    <t>e_NO5-400_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_008</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_033</t>
-  </si>
-  <si>
-    <t>e_NO27-420_NOR,e_w254428135-420_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_029</t>
-  </si>
-  <si>
-    <t>e_r8473044-220_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_026</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_013</t>
   </si>
   <si>
     <t>e_won_NOR_001</t>
@@ -6433,7 +6433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27583822-976E-4152-954F-D01ED48F89E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3DAC10-74E3-46A7-9CC0-C9424D8CC94B}">
   <dimension ref="B9:BD46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6671,16 +6671,16 @@
         <v>211</v>
       </c>
       <c r="Y11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z11" t="s">
         <v>235</v>
       </c>
       <c r="AA11">
-        <v>0.99882847078053061</v>
+        <v>0.99895143703583655</v>
       </c>
       <c r="AB11">
-        <v>21.478035690271827</v>
+        <v>19.223654342996348</v>
       </c>
       <c r="AD11" t="s">
         <v>210</v>
@@ -6710,13 +6710,13 @@
         <v>262</v>
       </c>
       <c r="AN11" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="AO11">
-        <v>0.99876487267473824</v>
+        <v>0.99826505593505321</v>
       </c>
       <c r="AP11">
-        <v>22.64400096313291</v>
+        <v>31.807307857358317</v>
       </c>
       <c r="AR11" t="s">
         <v>210</v>
@@ -6817,16 +6817,16 @@
         <v>215</v>
       </c>
       <c r="Y12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Z12" t="s">
         <v>236</v>
       </c>
       <c r="AA12">
-        <v>0.99575016499253088</v>
+        <v>0.99839397127563723</v>
       </c>
       <c r="AB12">
-        <v>77.913641803599788</v>
+        <v>29.44385994665101</v>
       </c>
       <c r="AD12" t="s">
         <v>210</v>
@@ -6853,16 +6853,16 @@
         <v>244</v>
       </c>
       <c r="AM12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN12" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="AO12">
-        <v>0.99964145023420503</v>
+        <v>0.99879556660280355</v>
       </c>
       <c r="AP12">
-        <v>6.5734123729074465</v>
+        <v>22.081278948601042</v>
       </c>
       <c r="AR12" t="s">
         <v>210</v>
@@ -6892,13 +6892,13 @@
         <v>351</v>
       </c>
       <c r="BB12" t="s">
-        <v>352</v>
+        <v>240</v>
       </c>
       <c r="BC12">
-        <v>0.98933754518059658</v>
+        <v>0.99160660811081658</v>
       </c>
       <c r="BD12">
-        <v>195.47833835572942</v>
+        <v>153.87885130169599</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6963,16 +6963,16 @@
         <v>217</v>
       </c>
       <c r="Y13" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Z13" t="s">
         <v>237</v>
       </c>
       <c r="AA13">
-        <v>0.99772047083431703</v>
+        <v>0.99575016499253088</v>
       </c>
       <c r="AB13">
-        <v>41.791368037520947</v>
+        <v>77.913641803599788</v>
       </c>
       <c r="AD13" t="s">
         <v>210</v>
@@ -6999,16 +6999,16 @@
         <v>246</v>
       </c>
       <c r="AM13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN13" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO13">
-        <v>0.99826505593505321</v>
+        <v>0.99841640215354499</v>
       </c>
       <c r="AP13">
-        <v>31.807307857358317</v>
+        <v>29.032627185008565</v>
       </c>
       <c r="AR13" t="s">
         <v>210</v>
@@ -7035,16 +7035,16 @@
         <v>281</v>
       </c>
       <c r="BA13" t="s">
+        <v>352</v>
+      </c>
+      <c r="BB13" t="s">
         <v>353</v>
       </c>
-      <c r="BB13" t="s">
-        <v>354</v>
-      </c>
       <c r="BC13">
-        <v>0.99263092479256698</v>
+        <v>0.9915629183169814</v>
       </c>
       <c r="BD13">
-        <v>135.09971213627173</v>
+        <v>154.67983085534144</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7109,16 +7109,16 @@
         <v>219</v>
       </c>
       <c r="Y14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Z14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AA14">
-        <v>0.99808381962859305</v>
+        <v>0.99772047083431703</v>
       </c>
       <c r="AB14">
-        <v>35.129973475794912</v>
+        <v>41.791368037520947</v>
       </c>
       <c r="AD14" t="s">
         <v>210</v>
@@ -7145,16 +7145,16 @@
         <v>248</v>
       </c>
       <c r="AM14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN14" t="s">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="AO14">
-        <v>0.99879556660280355</v>
+        <v>0.99820448750458923</v>
       </c>
       <c r="AP14">
-        <v>22.081278948601042</v>
+        <v>32.91772908253018</v>
       </c>
       <c r="AR14" t="s">
         <v>210</v>
@@ -7181,16 +7181,16 @@
         <v>283</v>
       </c>
       <c r="BA14" t="s">
+        <v>354</v>
+      </c>
+      <c r="BB14" t="s">
         <v>355</v>
       </c>
-      <c r="BB14" t="s">
-        <v>352</v>
-      </c>
       <c r="BC14">
-        <v>0.9735302461515426</v>
+        <v>0.96838022096107534</v>
       </c>
       <c r="BD14">
-        <v>485.2788205550533</v>
+        <v>579.69594904695282</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7255,16 +7255,16 @@
         <v>221</v>
       </c>
       <c r="Y15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Z15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AA15">
-        <v>0.99895143703583655</v>
+        <v>0.99808381962859305</v>
       </c>
       <c r="AB15">
-        <v>19.223654342996348</v>
+        <v>35.129973475794912</v>
       </c>
       <c r="AD15" t="s">
         <v>210</v>
@@ -7291,16 +7291,16 @@
         <v>250</v>
       </c>
       <c r="AM15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AN15" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="AO15">
-        <v>0.99797671409285116</v>
+        <v>0.99829640811481757</v>
       </c>
       <c r="AP15">
-        <v>37.093574964395906</v>
+        <v>31.232517895012144</v>
       </c>
       <c r="AR15" t="s">
         <v>210</v>
@@ -7330,13 +7330,13 @@
         <v>356</v>
       </c>
       <c r="BB15" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="BC15">
-        <v>0.98663125284575504</v>
+        <v>0.98154698324453926</v>
       </c>
       <c r="BD15">
-        <v>245.09369782782457</v>
+        <v>338.30530718344716</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7401,16 +7401,16 @@
         <v>223</v>
       </c>
       <c r="Y16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Z16" t="s">
         <v>239</v>
       </c>
       <c r="AA16">
-        <v>0.99839397127563723</v>
+        <v>0.99907990948974823</v>
       </c>
       <c r="AB16">
-        <v>29.44385994665101</v>
+        <v>16.868326021282812</v>
       </c>
       <c r="AD16" t="s">
         <v>210</v>
@@ -7437,16 +7437,16 @@
         <v>252</v>
       </c>
       <c r="AM16" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN16" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
       <c r="AO16">
-        <v>0.99841640215354499</v>
+        <v>0.99797671409285116</v>
       </c>
       <c r="AP16">
-        <v>29.032627185008565</v>
+        <v>37.093574964395906</v>
       </c>
       <c r="AR16" t="s">
         <v>210</v>
@@ -7473,16 +7473,16 @@
         <v>287</v>
       </c>
       <c r="BA16" t="s">
+        <v>357</v>
+      </c>
+      <c r="BB16" t="s">
         <v>358</v>
       </c>
-      <c r="BB16" t="s">
-        <v>240</v>
-      </c>
       <c r="BC16">
-        <v>0.99797704648789787</v>
+        <v>0.97946796363902389</v>
       </c>
       <c r="BD16">
-        <v>37.087481055204883</v>
+        <v>376.42066661789517</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7547,16 +7547,16 @@
         <v>225</v>
       </c>
       <c r="Y17" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s">
         <v>240</v>
       </c>
       <c r="AA17">
-        <v>0.99861411826024438</v>
+        <v>0.99882847078053061</v>
       </c>
       <c r="AB17">
-        <v>25.407831895519109</v>
+        <v>21.478035690271827</v>
       </c>
       <c r="AD17" t="s">
         <v>210</v>
@@ -7583,16 +7583,16 @@
         <v>254</v>
       </c>
       <c r="AM17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN17" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AO17">
-        <v>0.99820448750458923</v>
+        <v>0.99881709761965065</v>
       </c>
       <c r="AP17">
-        <v>32.91772908253018</v>
+        <v>21.686543639737447</v>
       </c>
       <c r="AR17" t="s">
         <v>210</v>
@@ -7622,13 +7622,13 @@
         <v>359</v>
       </c>
       <c r="BB17" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="BC17">
-        <v>0.97980165720226331</v>
+        <v>0.98680057418415568</v>
       </c>
       <c r="BD17">
-        <v>370.30295129183952</v>
+        <v>241.9894732904786</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7693,16 +7693,16 @@
         <v>227</v>
       </c>
       <c r="Y18" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="Z18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA18">
-        <v>0.99600812242405146</v>
+        <v>0.99861411826024438</v>
       </c>
       <c r="AB18">
-        <v>73.184422225722628</v>
+        <v>25.407831895519109</v>
       </c>
       <c r="AD18" t="s">
         <v>210</v>
@@ -7729,16 +7729,16 @@
         <v>256</v>
       </c>
       <c r="AM18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO18">
-        <v>0.99829640811481757</v>
+        <v>0.99788960803391069</v>
       </c>
       <c r="AP18">
-        <v>31.232517895012144</v>
+        <v>38.69051937830465</v>
       </c>
       <c r="AR18" t="s">
         <v>210</v>
@@ -7765,16 +7765,16 @@
         <v>291</v>
       </c>
       <c r="BA18" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="BB18" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="BC18">
-        <v>0.98702443219639058</v>
+        <v>0.99263092479256698</v>
       </c>
       <c r="BD18">
-        <v>237.88540973283864</v>
+        <v>135.09971213627173</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7839,16 +7839,16 @@
         <v>229</v>
       </c>
       <c r="Y19" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="Z19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AA19">
-        <v>0.99815562054185902</v>
+        <v>0.99600812242405146</v>
       </c>
       <c r="AB19">
-        <v>33.81362339925078</v>
+        <v>73.184422225722628</v>
       </c>
       <c r="AD19" t="s">
         <v>210</v>
@@ -7875,16 +7875,16 @@
         <v>258</v>
       </c>
       <c r="AM19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AN19" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="AO19">
-        <v>0.99788960803391069</v>
+        <v>0.99876487267473824</v>
       </c>
       <c r="AP19">
-        <v>38.69051937830465</v>
+        <v>22.64400096313291</v>
       </c>
       <c r="AR19" t="s">
         <v>210</v>
@@ -7911,16 +7911,16 @@
         <v>293</v>
       </c>
       <c r="BA19" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="BB19" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="BC19">
-        <v>0.98476539237821181</v>
+        <v>0.9735302461515426</v>
       </c>
       <c r="BD19">
-        <v>279.30113973278407</v>
+        <v>485.2788205550533</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7985,16 +7985,16 @@
         <v>231</v>
       </c>
       <c r="Y20" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Z20" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AA20">
-        <v>0.99907990948974823</v>
+        <v>0.99815562054185902</v>
       </c>
       <c r="AB20">
-        <v>16.868326021282812</v>
+        <v>33.81362339925078</v>
       </c>
       <c r="AD20" t="s">
         <v>210</v>
@@ -8024,13 +8024,13 @@
         <v>276</v>
       </c>
       <c r="AN20" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="AO20">
-        <v>0.99881709761965065</v>
+        <v>0.99964145023420503</v>
       </c>
       <c r="AP20">
-        <v>21.686543639737447</v>
+        <v>6.5734123729074465</v>
       </c>
       <c r="AR20" t="s">
         <v>210</v>
@@ -8057,16 +8057,16 @@
         <v>295</v>
       </c>
       <c r="BA20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="BB20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="BC20">
-        <v>0.99415783676882774</v>
+        <v>0.98673181208908134</v>
       </c>
       <c r="BD20">
-        <v>107.10632590482507</v>
+        <v>243.25011170017518</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8095,16 +8095,16 @@
         <v>297</v>
       </c>
       <c r="BA21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="BB21" t="s">
-        <v>239</v>
+        <v>360</v>
       </c>
       <c r="BC21">
-        <v>0.99504227556735247</v>
+        <v>0.98356866932261144</v>
       </c>
       <c r="BD21">
-        <v>90.891614598538183</v>
+        <v>301.24106241879042</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8133,16 +8133,16 @@
         <v>299</v>
       </c>
       <c r="BA22" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="BB22" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="BC22">
-        <v>0.98895989498625159</v>
+        <v>0.98444845125527902</v>
       </c>
       <c r="BD22">
-        <v>202.40192525205526</v>
+        <v>285.11172698655224</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8174,13 +8174,13 @@
         <v>368</v>
       </c>
       <c r="BB23" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="BC23">
-        <v>0.9946795421707223</v>
+        <v>0.98702443219639058</v>
       </c>
       <c r="BD23">
-        <v>97.541726870091992</v>
+        <v>237.88540973283864</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8209,16 +8209,16 @@
         <v>303</v>
       </c>
       <c r="BA24" t="s">
+        <v>369</v>
+      </c>
+      <c r="BB24" t="s">
         <v>370</v>
       </c>
-      <c r="BB24" t="s">
-        <v>352</v>
-      </c>
       <c r="BC24">
-        <v>0.99203628399018684</v>
+        <v>0.98476539237821181</v>
       </c>
       <c r="BD24">
-        <v>146.0014601799073</v>
+        <v>279.30113973278407</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8253,10 +8253,10 @@
         <v>372</v>
       </c>
       <c r="BC25">
-        <v>0.99736616273496814</v>
+        <v>0.99415783676882774</v>
       </c>
       <c r="BD25">
-        <v>48.287016525584328</v>
+        <v>107.10632590482507</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8288,13 +8288,13 @@
         <v>373</v>
       </c>
       <c r="BB26" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="BC26">
-        <v>0.9970758558134436</v>
+        <v>0.99504227556735247</v>
       </c>
       <c r="BD26">
-        <v>53.609310086867303</v>
+        <v>90.891614598538183</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8329,10 +8329,10 @@
         <v>375</v>
       </c>
       <c r="BC27">
-        <v>0.99084956331481444</v>
+        <v>0.98663125284575504</v>
       </c>
       <c r="BD27">
-        <v>167.75800589506906</v>
+        <v>245.09369782782457</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8364,13 +8364,13 @@
         <v>376</v>
       </c>
       <c r="BB28" t="s">
-        <v>352</v>
+        <v>241</v>
       </c>
       <c r="BC28">
-        <v>0.97270723841704188</v>
+        <v>0.99797704648789787</v>
       </c>
       <c r="BD28">
-        <v>500.36729568756573</v>
+        <v>37.087481055204883</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8402,13 +8402,13 @@
         <v>377</v>
       </c>
       <c r="BB29" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="BC29">
-        <v>0.97946796363902389</v>
+        <v>0.97980165720226331</v>
       </c>
       <c r="BD29">
-        <v>376.42066661789517</v>
+        <v>370.30295129183952</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -8437,16 +8437,16 @@
         <v>315</v>
       </c>
       <c r="BA30" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="BB30" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="BC30">
-        <v>0.98680057418415568</v>
+        <v>0.97883706818412031</v>
       </c>
       <c r="BD30">
-        <v>241.9894732904786</v>
+        <v>387.9870832911281</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -8475,16 +8475,16 @@
         <v>317</v>
       </c>
       <c r="BA31" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="BB31" t="s">
-        <v>357</v>
+        <v>241</v>
       </c>
       <c r="BC31">
-        <v>0.97883706818412031</v>
+        <v>0.98028383834588584</v>
       </c>
       <c r="BD31">
-        <v>387.9870832911281</v>
+        <v>361.46296365875969</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -8513,16 +8513,16 @@
         <v>319</v>
       </c>
       <c r="BA32" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="BB32" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="BC32">
-        <v>0.98028383834588584</v>
+        <v>0.99011129922618213</v>
       </c>
       <c r="BD32">
-        <v>361.46296365875969</v>
+        <v>181.29284751999512</v>
       </c>
     </row>
     <row r="33" spans="44:56">
@@ -8551,16 +8551,16 @@
         <v>321</v>
       </c>
       <c r="BA33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BB33" t="s">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="BC33">
-        <v>0.99011129922618213</v>
+        <v>0.98774608354852067</v>
       </c>
       <c r="BD33">
-        <v>181.29284751999512</v>
+        <v>224.6551349437874</v>
       </c>
     </row>
     <row r="34" spans="44:56">
@@ -8589,16 +8589,16 @@
         <v>323</v>
       </c>
       <c r="BA34" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="BB34" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="BC34">
-        <v>0.98774608354852067</v>
+        <v>0.9898072805035012</v>
       </c>
       <c r="BD34">
-        <v>224.6551349437874</v>
+        <v>186.86652410247837</v>
       </c>
     </row>
     <row r="35" spans="44:56">
@@ -8627,16 +8627,16 @@
         <v>325</v>
       </c>
       <c r="BA35" t="s">
+        <v>383</v>
+      </c>
+      <c r="BB35" t="s">
         <v>384</v>
       </c>
-      <c r="BB35" t="s">
-        <v>352</v>
-      </c>
       <c r="BC35">
-        <v>0.9898072805035012</v>
+        <v>0.99409227633736386</v>
       </c>
       <c r="BD35">
-        <v>186.86652410247837</v>
+        <v>108.3082671483288</v>
       </c>
     </row>
     <row r="36" spans="44:56">
@@ -8671,10 +8671,10 @@
         <v>386</v>
       </c>
       <c r="BC36">
-        <v>0.98673181208908134</v>
+        <v>0.98616712629287406</v>
       </c>
       <c r="BD36">
-        <v>243.25011170017518</v>
+        <v>253.60268463064131</v>
       </c>
     </row>
     <row r="37" spans="44:56">
@@ -8706,13 +8706,13 @@
         <v>387</v>
       </c>
       <c r="BB37" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="BC37">
-        <v>0.98356866932261144</v>
+        <v>0.99132349157736788</v>
       </c>
       <c r="BD37">
-        <v>301.24106241879042</v>
+        <v>159.06932108158975</v>
       </c>
     </row>
     <row r="38" spans="44:56">
@@ -8744,13 +8744,13 @@
         <v>388</v>
       </c>
       <c r="BB38" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="BC38">
-        <v>0.98444845125527902</v>
+        <v>0.97511664185498959</v>
       </c>
       <c r="BD38">
-        <v>285.11172698655224</v>
+        <v>456.19489932519053</v>
       </c>
     </row>
     <row r="39" spans="44:56">
@@ -8782,13 +8782,13 @@
         <v>389</v>
       </c>
       <c r="BB39" t="s">
-        <v>235</v>
+        <v>390</v>
       </c>
       <c r="BC39">
-        <v>0.99160660811081658</v>
+        <v>0.99736616273496814</v>
       </c>
       <c r="BD39">
-        <v>153.87885130169599</v>
+        <v>48.287016525584328</v>
       </c>
     </row>
     <row r="40" spans="44:56">
@@ -8817,16 +8817,16 @@
         <v>335</v>
       </c>
       <c r="BA40" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="BB40" t="s">
-        <v>391</v>
+        <v>270</v>
       </c>
       <c r="BC40">
-        <v>0.9915629183169814</v>
+        <v>0.9970758558134436</v>
       </c>
       <c r="BD40">
-        <v>154.67983085534144</v>
+        <v>53.609310086867303</v>
       </c>
     </row>
     <row r="41" spans="44:56">
@@ -8861,10 +8861,10 @@
         <v>393</v>
       </c>
       <c r="BC41">
-        <v>0.96838022096107534</v>
+        <v>0.99084956331481444</v>
       </c>
       <c r="BD41">
-        <v>579.69594904695282</v>
+        <v>167.75800589506906</v>
       </c>
     </row>
     <row r="42" spans="44:56">
@@ -8896,13 +8896,13 @@
         <v>394</v>
       </c>
       <c r="BB42" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="BC42">
-        <v>0.98154698324453926</v>
+        <v>0.97270723841704188</v>
       </c>
       <c r="BD42">
-        <v>338.30530718344716</v>
+        <v>500.36729568756573</v>
       </c>
     </row>
     <row r="43" spans="44:56">
@@ -8937,10 +8937,10 @@
         <v>396</v>
       </c>
       <c r="BC43">
-        <v>0.99409227633736386</v>
+        <v>0.98895989498625159</v>
       </c>
       <c r="BD43">
-        <v>108.3082671483288</v>
+        <v>202.40192525205526</v>
       </c>
     </row>
     <row r="44" spans="44:56">
@@ -8975,10 +8975,10 @@
         <v>398</v>
       </c>
       <c r="BC44">
-        <v>0.98616712629287406</v>
+        <v>0.9946795421707223</v>
       </c>
       <c r="BD44">
-        <v>253.60268463064131</v>
+        <v>97.541726870091992</v>
       </c>
     </row>
     <row r="45" spans="44:56">
@@ -9010,13 +9010,13 @@
         <v>399</v>
       </c>
       <c r="BB45" t="s">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="BC45">
-        <v>0.99132349157736788</v>
+        <v>0.99203628399018684</v>
       </c>
       <c r="BD45">
-        <v>159.06932108158975</v>
+        <v>146.0014601799073</v>
       </c>
     </row>
     <row r="46" spans="44:56">
@@ -9048,13 +9048,13 @@
         <v>400</v>
       </c>
       <c r="BB46" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="BC46">
-        <v>0.97511664185498959</v>
+        <v>0.98933754518059658</v>
       </c>
       <c r="BD46">
-        <v>456.19489932519053</v>
+        <v>195.47833835572942</v>
       </c>
     </row>
   </sheetData>
@@ -9063,7 +9063,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59FF34CB-6890-4BF0-A7DE-AE153C3DCAF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1950B27A-9399-4C9F-AECF-49A62E28044A}">
   <dimension ref="B9:Z46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9175,7 +9175,7 @@
         <v>401</v>
       </c>
       <c r="K11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L11">
         <v>9.3983953427017717</v>
@@ -9208,7 +9208,7 @@
         <v>421</v>
       </c>
       <c r="X11" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="Y11">
         <v>175.143</v>
@@ -9243,7 +9243,7 @@
         <v>403</v>
       </c>
       <c r="K12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L12">
         <v>13.625732114073267</v>
@@ -9276,7 +9276,7 @@
         <v>423</v>
       </c>
       <c r="X12" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="Y12">
         <v>80.552999999999997</v>
@@ -9311,7 +9311,7 @@
         <v>405</v>
       </c>
       <c r="K13" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="L13">
         <v>4.6051004861597438</v>
@@ -9344,7 +9344,7 @@
         <v>425</v>
       </c>
       <c r="X13" t="s">
-        <v>351</v>
+        <v>400</v>
       </c>
       <c r="Y13">
         <v>122.583</v>
@@ -9379,7 +9379,7 @@
         <v>407</v>
       </c>
       <c r="K14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L14">
         <v>33.306493435672031</v>
@@ -9412,7 +9412,7 @@
         <v>427</v>
       </c>
       <c r="X14" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="Y14">
         <v>9.1065000000000005</v>
@@ -9447,7 +9447,7 @@
         <v>409</v>
       </c>
       <c r="K15" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L15">
         <v>28.124383953079484</v>
@@ -9480,7 +9480,7 @@
         <v>429</v>
       </c>
       <c r="X15" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="Y15">
         <v>29.298749999999998</v>
@@ -9515,7 +9515,7 @@
         <v>411</v>
       </c>
       <c r="K16" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="L16">
         <v>8.0206658660488124</v>
@@ -9548,7 +9548,7 @@
         <v>431</v>
       </c>
       <c r="X16" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="Y16">
         <v>80.770499999999998</v>
@@ -9583,7 +9583,7 @@
         <v>413</v>
       </c>
       <c r="K17" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L17">
         <v>3.7261534166349795</v>
@@ -9616,7 +9616,7 @@
         <v>433</v>
       </c>
       <c r="X17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Y17">
         <v>107.307</v>
@@ -9651,7 +9651,7 @@
         <v>415</v>
       </c>
       <c r="K18" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L18">
         <v>26.672003507855468</v>
@@ -9684,7 +9684,7 @@
         <v>435</v>
       </c>
       <c r="X18" t="s">
-        <v>394</v>
+        <v>356</v>
       </c>
       <c r="Y18">
         <v>161.3595</v>
@@ -9719,7 +9719,7 @@
         <v>417</v>
       </c>
       <c r="K19" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L19">
         <v>28.011000950183487</v>
@@ -9752,7 +9752,7 @@
         <v>437</v>
       </c>
       <c r="X19" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="Y19">
         <v>17.402249999999999</v>
@@ -9787,7 +9787,7 @@
         <v>419</v>
       </c>
       <c r="K20" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L20">
         <v>19.93200133031517</v>
@@ -9820,7 +9820,7 @@
         <v>439</v>
       </c>
       <c r="X20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Y20">
         <v>107.56874999999999</v>
@@ -9890,7 +9890,7 @@
         <v>443</v>
       </c>
       <c r="X22" t="s">
-        <v>392</v>
+        <v>354</v>
       </c>
       <c r="Y22">
         <v>112.0095</v>
@@ -9925,7 +9925,7 @@
         <v>445</v>
       </c>
       <c r="X23" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="Y23">
         <v>78.981750000000005</v>
@@ -9960,7 +9960,7 @@
         <v>447</v>
       </c>
       <c r="X24" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="Y24">
         <v>91.574250000000006</v>
@@ -9995,7 +9995,7 @@
         <v>449</v>
       </c>
       <c r="X25" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="Y25">
         <v>118.12350000000001</v>
@@ -10030,7 +10030,7 @@
         <v>451</v>
       </c>
       <c r="X26" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="Y26">
         <v>91.725750000000005</v>
@@ -10065,7 +10065,7 @@
         <v>453</v>
       </c>
       <c r="X27" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="Y27">
         <v>183.10175000000001</v>
@@ -10100,7 +10100,7 @@
         <v>455</v>
       </c>
       <c r="X28" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="Y28">
         <v>21.253499999999999</v>
@@ -10135,7 +10135,7 @@
         <v>457</v>
       </c>
       <c r="X29" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="Y29">
         <v>52.41375</v>
@@ -10170,7 +10170,7 @@
         <v>459</v>
       </c>
       <c r="X30" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="Y30">
         <v>20.409749999999999</v>
@@ -10205,7 +10205,7 @@
         <v>461</v>
       </c>
       <c r="X31" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="Y31">
         <v>130.00049999999999</v>
@@ -10240,7 +10240,7 @@
         <v>463</v>
       </c>
       <c r="X32" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y32">
         <v>113.55374999999999</v>
@@ -10275,7 +10275,7 @@
         <v>465</v>
       </c>
       <c r="X33" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="Y33">
         <v>34.866</v>
@@ -10310,7 +10310,7 @@
         <v>467</v>
       </c>
       <c r="X34" t="s">
-        <v>389</v>
+        <v>351</v>
       </c>
       <c r="Y34">
         <v>121.57675</v>
@@ -10345,7 +10345,7 @@
         <v>469</v>
       </c>
       <c r="X35" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="Y35">
         <v>23.104500000000002</v>
@@ -10380,7 +10380,7 @@
         <v>471</v>
       </c>
       <c r="X36" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="Y36">
         <v>38.839500000000001</v>
@@ -10415,7 +10415,7 @@
         <v>473</v>
       </c>
       <c r="X37" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="Y37">
         <v>45.419249999999998</v>
@@ -10450,7 +10450,7 @@
         <v>475</v>
       </c>
       <c r="X38" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="Y38">
         <v>39.345750000000002</v>
@@ -10485,7 +10485,7 @@
         <v>477</v>
       </c>
       <c r="X39" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="Y39">
         <v>95.484750000000005</v>
@@ -10520,7 +10520,7 @@
         <v>479</v>
       </c>
       <c r="X40" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="Y40">
         <v>145.971</v>
@@ -10555,7 +10555,7 @@
         <v>481</v>
       </c>
       <c r="X41" t="s">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="Y41">
         <v>77.473500000000001</v>
@@ -10590,7 +10590,7 @@
         <v>483</v>
       </c>
       <c r="X42" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="Y42">
         <v>63.514499999999998</v>
@@ -10625,7 +10625,7 @@
         <v>485</v>
       </c>
       <c r="X43" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="Y43">
         <v>71.952749999999995</v>
@@ -10660,7 +10660,7 @@
         <v>487</v>
       </c>
       <c r="X44" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Y44">
         <v>155.05350000000001</v>
@@ -10695,7 +10695,7 @@
         <v>489</v>
       </c>
       <c r="X45" t="s">
-        <v>390</v>
+        <v>352</v>
       </c>
       <c r="Y45">
         <v>68.032499999999999</v>
@@ -10730,7 +10730,7 @@
         <v>491</v>
       </c>
       <c r="X46" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="Y46">
         <v>77.678250000000006</v>
@@ -10745,7 +10745,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A354A63-47A5-49A4-A244-5DD9E0D7B071}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C703473A-69A4-4C27-97D8-74D4DD042E46}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
